--- a/backend/data/financials_by_company/0976.HK.xlsx
+++ b/backend/data/financials_by_company/0976.HK.xlsx
@@ -657,55 +657,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>4785000</v>
+        <v>18786035.985063</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.216929</v>
       </c>
       <c r="D2" t="n">
-        <v>597100000</v>
+        <v>1447100000</v>
       </c>
       <c r="E2" t="n">
-        <v>29000000</v>
+        <v>86600000</v>
       </c>
       <c r="F2" t="n">
-        <v>29000000</v>
+        <v>86600000</v>
       </c>
       <c r="G2" t="n">
-        <v>-9300000</v>
+        <v>702000000</v>
       </c>
       <c r="H2" t="n">
-        <v>390200000</v>
+        <v>406700000</v>
       </c>
       <c r="I2" t="n">
-        <v>15441700000</v>
+        <v>20061900000</v>
       </c>
       <c r="J2" t="n">
-        <v>626100000</v>
+        <v>1533700000</v>
       </c>
       <c r="K2" t="n">
-        <v>235900000</v>
+        <v>1127000000</v>
       </c>
       <c r="L2" t="n">
-        <v>-181700000</v>
+        <v>-233800000</v>
       </c>
       <c r="M2" t="n">
-        <v>186600000</v>
+        <v>243300000</v>
       </c>
       <c r="N2" t="n">
-        <v>4900000</v>
+        <v>9500000</v>
       </c>
       <c r="O2" t="n">
-        <v>-33515000</v>
+        <v>634186035.985063</v>
       </c>
       <c r="P2" t="n">
-        <v>-9300000</v>
+        <v>702000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>16368200000</v>
+        <v>21281700000</v>
       </c>
       <c r="R2" t="n">
         <v>1605152000</v>
@@ -714,88 +714,88 @@
         <v>1605152000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01</v>
+        <v>0.44</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.01</v>
+        <v>0.44</v>
       </c>
       <c r="V2" t="n">
-        <v>-9300000</v>
+        <v>702000000</v>
       </c>
       <c r="W2" t="n">
-        <v>-9300000</v>
+        <v>702000000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-9300000</v>
+        <v>702000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>9900000</v>
+        <v>10000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-19200000</v>
+        <v>692000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-19200000</v>
+        <v>692000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>68500000</v>
+        <v>191700000</v>
       </c>
       <c r="AD2" t="n">
-        <v>49300000</v>
+        <v>883700000</v>
       </c>
       <c r="AE2" t="n">
-        <v>45600000</v>
+        <v>39000000</v>
       </c>
       <c r="AF2" t="n">
-        <v>33600000</v>
+        <v>83900000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-45500000</v>
+        <v>-146400000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-23700000</v>
+        <v>40200000</v>
       </c>
       <c r="AI2" t="n">
-        <v>35600000</v>
+        <v>22300000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-181700000</v>
+        <v>-233800000</v>
       </c>
       <c r="AK2" t="n">
-        <v>186600000</v>
+        <v>243300000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4900000</v>
+        <v>9500000</v>
       </c>
       <c r="AM2" t="n">
-        <v>111500000</v>
+        <v>668700000</v>
       </c>
       <c r="AN2" t="n">
-        <v>926500000</v>
+        <v>1219800000</v>
       </c>
       <c r="AO2" t="n">
-        <v>955400000</v>
+        <v>1245700000</v>
       </c>
       <c r="AP2" t="n">
-        <v>48200000</v>
+        <v>59900000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>907200000</v>
+        <v>1185800000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1038000000</v>
+        <v>1888500000</v>
       </c>
       <c r="AS2" t="n">
-        <v>15441700000</v>
+        <v>20061900000</v>
       </c>
       <c r="AT2" t="n">
-        <v>16479700000</v>
+        <v>21950400000</v>
       </c>
       <c r="AU2" t="n">
-        <v>16479700000</v>
+        <v>21950400000</v>
       </c>
     </row>
     <row r="3">
@@ -943,55 +943,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>18786035.985063</v>
+        <v>4785000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.216929</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>1447100000</v>
+        <v>597100000</v>
       </c>
       <c r="E4" t="n">
-        <v>86600000</v>
+        <v>29000000</v>
       </c>
       <c r="F4" t="n">
-        <v>86600000</v>
+        <v>29000000</v>
       </c>
       <c r="G4" t="n">
-        <v>702000000</v>
+        <v>-9300000</v>
       </c>
       <c r="H4" t="n">
-        <v>406700000</v>
+        <v>390200000</v>
       </c>
       <c r="I4" t="n">
-        <v>20061900000</v>
+        <v>15441700000</v>
       </c>
       <c r="J4" t="n">
-        <v>1533700000</v>
+        <v>626100000</v>
       </c>
       <c r="K4" t="n">
-        <v>1127000000</v>
+        <v>235900000</v>
       </c>
       <c r="L4" t="n">
-        <v>-233800000</v>
+        <v>-181700000</v>
       </c>
       <c r="M4" t="n">
-        <v>243300000</v>
+        <v>186600000</v>
       </c>
       <c r="N4" t="n">
-        <v>9500000</v>
+        <v>4900000</v>
       </c>
       <c r="O4" t="n">
-        <v>634186035.985063</v>
+        <v>-33515000</v>
       </c>
       <c r="P4" t="n">
-        <v>702000000</v>
+        <v>-9300000</v>
       </c>
       <c r="Q4" t="n">
-        <v>21281700000</v>
+        <v>16368200000</v>
       </c>
       <c r="R4" t="n">
         <v>1605152000</v>
@@ -1000,88 +1000,88 @@
         <v>1605152000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="V4" t="n">
-        <v>702000000</v>
+        <v>-9300000</v>
       </c>
       <c r="W4" t="n">
-        <v>702000000</v>
+        <v>-9300000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>702000000</v>
+        <v>-9300000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10000000</v>
+        <v>9900000</v>
       </c>
       <c r="AA4" t="n">
-        <v>692000000</v>
+        <v>-19200000</v>
       </c>
       <c r="AB4" t="n">
-        <v>692000000</v>
+        <v>-19200000</v>
       </c>
       <c r="AC4" t="n">
-        <v>191700000</v>
+        <v>68500000</v>
       </c>
       <c r="AD4" t="n">
-        <v>883700000</v>
+        <v>49300000</v>
       </c>
       <c r="AE4" t="n">
-        <v>39000000</v>
+        <v>45600000</v>
       </c>
       <c r="AF4" t="n">
-        <v>83900000</v>
+        <v>33600000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-146400000</v>
+        <v>-45500000</v>
       </c>
       <c r="AH4" t="n">
-        <v>40200000</v>
+        <v>-23700000</v>
       </c>
       <c r="AI4" t="n">
-        <v>22300000</v>
+        <v>35600000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-233800000</v>
+        <v>-181700000</v>
       </c>
       <c r="AK4" t="n">
-        <v>243300000</v>
+        <v>186600000</v>
       </c>
       <c r="AL4" t="n">
-        <v>9500000</v>
+        <v>4900000</v>
       </c>
       <c r="AM4" t="n">
-        <v>668700000</v>
+        <v>111500000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1219800000</v>
+        <v>926500000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1245700000</v>
+        <v>955400000</v>
       </c>
       <c r="AP4" t="n">
-        <v>59900000</v>
+        <v>48200000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1185800000</v>
+        <v>907200000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1888500000</v>
+        <v>1038000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>20061900000</v>
+        <v>15441700000</v>
       </c>
       <c r="AT4" t="n">
-        <v>21950400000</v>
+        <v>16479700000</v>
       </c>
       <c r="AU4" t="n">
-        <v>21950400000</v>
+        <v>16479700000</v>
       </c>
     </row>
   </sheetData>
@@ -1472,7 +1472,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1605152291</v>
@@ -1481,47 +1481,45 @@
         <v>1605152291</v>
       </c>
       <c r="D2" t="n">
-        <v>536600000</v>
+        <v>879600000</v>
       </c>
       <c r="E2" t="n">
-        <v>1264900000</v>
+        <v>2029100000</v>
       </c>
       <c r="F2" t="n">
-        <v>4138000000</v>
+        <v>4025000000</v>
       </c>
       <c r="G2" t="n">
-        <v>5834600000</v>
+        <v>6535800000</v>
       </c>
       <c r="H2" t="n">
-        <v>1026900000</v>
+        <v>575000000</v>
       </c>
       <c r="I2" t="n">
-        <v>4138000000</v>
+        <v>4025000000</v>
       </c>
       <c r="J2" t="n">
-        <v>361800000</v>
+        <v>367200000</v>
       </c>
       <c r="K2" t="n">
-        <v>4931500000</v>
+        <v>4873900000</v>
       </c>
       <c r="L2" t="n">
-        <v>5048100000</v>
+        <v>4924700000</v>
       </c>
       <c r="M2" t="n">
-        <v>4874500000</v>
+        <v>4859500000</v>
       </c>
       <c r="N2" t="n">
-        <v>-57000000</v>
+        <v>-14400000</v>
       </c>
       <c r="O2" t="n">
-        <v>4931500000</v>
+        <v>4873900000</v>
       </c>
       <c r="P2" t="n">
-        <v>-1591100000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5912200000</v>
-      </c>
+        <v>-1846300000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>16100000</v>
       </c>
@@ -1529,161 +1527,173 @@
         <v>16100000</v>
       </c>
       <c r="T2" t="n">
-        <v>3845900000</v>
+        <v>5099000000</v>
       </c>
       <c r="U2" t="n">
-        <v>759900000</v>
+        <v>672400000</v>
       </c>
       <c r="V2" t="n">
-        <v>9800000</v>
+        <v>18900000</v>
       </c>
       <c r="W2" t="n">
-        <v>30200000</v>
+        <v>37300000</v>
       </c>
       <c r="X2" t="n">
-        <v>285400000</v>
+        <v>305800000</v>
       </c>
       <c r="Y2" t="n">
-        <v>363600000</v>
+        <v>240900000</v>
       </c>
       <c r="Z2" t="n">
-        <v>247000000</v>
+        <v>190100000</v>
       </c>
       <c r="AA2" t="n">
-        <v>116600000</v>
+        <v>50800000</v>
       </c>
       <c r="AB2" t="n">
-        <v>70900000</v>
+        <v>69500000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3086000000</v>
+        <v>4426600000</v>
       </c>
       <c r="AD2" t="n">
-        <v>901300000</v>
+        <v>1788200000</v>
       </c>
       <c r="AE2" t="n">
-        <v>114800000</v>
+        <v>177100000</v>
       </c>
       <c r="AF2" t="n">
-        <v>786500000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>1611100000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3400000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>1916000000</v>
+        <v>2359800000</v>
       </c>
       <c r="AI2" t="n">
-        <v>184900000</v>
+        <v>250700000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>86300000</v>
+        <v>307800000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1644800000</v>
+        <v>1801300000</v>
       </c>
       <c r="AL2" t="n">
-        <v>8720400000</v>
+        <v>9958500000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4607500000</v>
+        <v>4956900000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7500000</v>
+        <v>14800000</v>
       </c>
       <c r="AO2" t="n">
-        <v>62300000</v>
+        <v>78900000</v>
       </c>
       <c r="AP2" t="n">
-        <v>88400000</v>
+        <v>92100000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>87600000</v>
+        <v>91300000</v>
       </c>
       <c r="AR2" t="n">
         <v>800000</v>
       </c>
       <c r="AS2" t="n">
-        <v>738300000</v>
+        <v>907800000</v>
       </c>
       <c r="AT2" t="n">
-        <v>49700000</v>
+        <v>56300000</v>
       </c>
       <c r="AU2" t="n">
-        <v>793500000</v>
+        <v>848900000</v>
       </c>
       <c r="AV2" t="n">
-        <v>261400000</v>
+        <v>294900000</v>
       </c>
       <c r="AW2" t="n">
-        <v>532100000</v>
+        <v>554000000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2867800000</v>
+        <v>2958100000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-4297600000</v>
+        <v>-1984000000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7165400000</v>
+        <v>4942100000</v>
       </c>
       <c r="BA2" t="n">
-        <v>70300000</v>
+        <v>47100000</v>
       </c>
       <c r="BB2" t="n">
-        <v>315800000</v>
+        <v>2489800000</v>
       </c>
       <c r="BC2" t="n">
-        <v>2741900000</v>
+        <v>1726700000</v>
       </c>
       <c r="BD2" t="n">
-        <v>601900000</v>
+        <v>678500000</v>
       </c>
       <c r="BE2" t="n">
-        <v>3435500000</v>
+        <v>2884900000</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>4112900000</v>
+        <v>5001600000</v>
       </c>
       <c r="BH2" t="n">
-        <v>16500000</v>
+        <v>31100000</v>
       </c>
       <c r="BI2" t="n">
-        <v>51700000</v>
+        <v>167000000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>142400000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>225800000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>1712200000</v>
+        <v>1567800000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1552700000</v>
+        <v>1377700000</v>
       </c>
       <c r="BN2" t="n">
-        <v>159500000</v>
+        <v>190100000</v>
       </c>
       <c r="BO2" t="n">
-        <v>85300000</v>
+        <v>66800000</v>
       </c>
       <c r="BP2" t="n">
-        <v>91100000</v>
+        <v>17300000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1784600000</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+        <v>2226900000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-55400000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1827100000</v>
+      </c>
       <c r="BT2" t="n">
-        <v>366500000</v>
+        <v>782300000</v>
       </c>
       <c r="BU2" t="n">
-        <v>366500000</v>
-      </c>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
+        <v>782300000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>777700000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1914,7 +1924,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1605152291</v>
@@ -1923,45 +1933,47 @@
         <v>1605152291</v>
       </c>
       <c r="D4" t="n">
-        <v>879600000</v>
+        <v>536600000</v>
       </c>
       <c r="E4" t="n">
-        <v>2029100000</v>
+        <v>1264900000</v>
       </c>
       <c r="F4" t="n">
-        <v>4025000000</v>
+        <v>4138000000</v>
       </c>
       <c r="G4" t="n">
-        <v>6535800000</v>
+        <v>5834600000</v>
       </c>
       <c r="H4" t="n">
-        <v>575000000</v>
+        <v>1026900000</v>
       </c>
       <c r="I4" t="n">
-        <v>4025000000</v>
+        <v>4138000000</v>
       </c>
       <c r="J4" t="n">
-        <v>367200000</v>
+        <v>361800000</v>
       </c>
       <c r="K4" t="n">
-        <v>4873900000</v>
+        <v>4931500000</v>
       </c>
       <c r="L4" t="n">
-        <v>4924700000</v>
+        <v>5048100000</v>
       </c>
       <c r="M4" t="n">
-        <v>4859500000</v>
+        <v>4874500000</v>
       </c>
       <c r="N4" t="n">
-        <v>-14400000</v>
+        <v>-57000000</v>
       </c>
       <c r="O4" t="n">
-        <v>4873900000</v>
+        <v>4931500000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1846300000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-1591100000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5912200000</v>
+      </c>
       <c r="R4" t="n">
         <v>16100000</v>
       </c>
@@ -1969,173 +1981,161 @@
         <v>16100000</v>
       </c>
       <c r="T4" t="n">
-        <v>5099000000</v>
+        <v>3845900000</v>
       </c>
       <c r="U4" t="n">
-        <v>672400000</v>
+        <v>759900000</v>
       </c>
       <c r="V4" t="n">
-        <v>18900000</v>
+        <v>9800000</v>
       </c>
       <c r="W4" t="n">
-        <v>37300000</v>
+        <v>30200000</v>
       </c>
       <c r="X4" t="n">
-        <v>305800000</v>
+        <v>285400000</v>
       </c>
       <c r="Y4" t="n">
-        <v>240900000</v>
+        <v>363600000</v>
       </c>
       <c r="Z4" t="n">
-        <v>190100000</v>
+        <v>247000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>50800000</v>
+        <v>116600000</v>
       </c>
       <c r="AB4" t="n">
-        <v>69500000</v>
+        <v>70900000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4426600000</v>
+        <v>3086000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1788200000</v>
+        <v>901300000</v>
       </c>
       <c r="AE4" t="n">
-        <v>177100000</v>
+        <v>114800000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1611100000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3400000</v>
-      </c>
+        <v>786500000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>2359800000</v>
+        <v>1916000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>250700000</v>
+        <v>184900000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>307800000</v>
+        <v>86300000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1801300000</v>
+        <v>1644800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>9958500000</v>
+        <v>8720400000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4956900000</v>
+        <v>4607500000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14800000</v>
+        <v>7500000</v>
       </c>
       <c r="AO4" t="n">
-        <v>78900000</v>
+        <v>62300000</v>
       </c>
       <c r="AP4" t="n">
-        <v>92100000</v>
+        <v>88400000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>91300000</v>
+        <v>87600000</v>
       </c>
       <c r="AR4" t="n">
         <v>800000</v>
       </c>
       <c r="AS4" t="n">
-        <v>907800000</v>
+        <v>738300000</v>
       </c>
       <c r="AT4" t="n">
-        <v>56300000</v>
+        <v>49700000</v>
       </c>
       <c r="AU4" t="n">
-        <v>848900000</v>
+        <v>793500000</v>
       </c>
       <c r="AV4" t="n">
-        <v>294900000</v>
+        <v>261400000</v>
       </c>
       <c r="AW4" t="n">
-        <v>554000000</v>
+        <v>532100000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2958100000</v>
+        <v>2867800000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1984000000</v>
+        <v>-4297600000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4942100000</v>
+        <v>7165400000</v>
       </c>
       <c r="BA4" t="n">
-        <v>47100000</v>
+        <v>70300000</v>
       </c>
       <c r="BB4" t="n">
-        <v>2489800000</v>
+        <v>315800000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1726700000</v>
+        <v>2741900000</v>
       </c>
       <c r="BD4" t="n">
-        <v>678500000</v>
+        <v>601900000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2884900000</v>
+        <v>3435500000</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>5001600000</v>
+        <v>4112900000</v>
       </c>
       <c r="BH4" t="n">
-        <v>31100000</v>
+        <v>16500000</v>
       </c>
       <c r="BI4" t="n">
-        <v>167000000</v>
+        <v>51700000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>142400000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>225800000</v>
-      </c>
+        <v>5000000</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>1567800000</v>
+        <v>1712200000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1377700000</v>
+        <v>1552700000</v>
       </c>
       <c r="BN4" t="n">
-        <v>190100000</v>
+        <v>159500000</v>
       </c>
       <c r="BO4" t="n">
-        <v>66800000</v>
+        <v>85300000</v>
       </c>
       <c r="BP4" t="n">
-        <v>17300000</v>
+        <v>91100000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2226900000</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>-55400000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1827100000</v>
-      </c>
+        <v>1784600000</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
-        <v>782300000</v>
+        <v>366500000</v>
       </c>
       <c r="BU4" t="n">
-        <v>782300000</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>777700000</v>
-      </c>
+        <v>366500000</v>
+      </c>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2395,147 +2395,147 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-259800000</v>
+        <v>241000000</v>
       </c>
       <c r="C2" t="n">
-        <v>-477900000</v>
+        <v>-1076800000</v>
       </c>
       <c r="D2" t="n">
-        <v>249600000</v>
+        <v>459500000</v>
       </c>
       <c r="E2" t="n">
-        <v>-212300000</v>
+        <v>-164700000</v>
       </c>
       <c r="F2" t="n">
-        <v>366500000</v>
+        <v>782300000</v>
       </c>
       <c r="G2" t="n">
-        <v>713700000</v>
+        <v>913800000</v>
       </c>
       <c r="H2" t="n">
-        <v>-29500000</v>
+        <v>-22400000</v>
       </c>
       <c r="I2" t="n">
-        <v>-317700000</v>
+        <v>-109100000</v>
       </c>
       <c r="J2" t="n">
-        <v>-330100000</v>
+        <v>-805400000</v>
       </c>
       <c r="K2" t="n">
-        <v>31400000</v>
+        <v>10600000</v>
       </c>
       <c r="L2" t="n">
-        <v>-228300000</v>
+        <v>-617300000</v>
       </c>
       <c r="M2" t="n">
-        <v>-228300000</v>
+        <v>-617300000</v>
       </c>
       <c r="N2" t="n">
-        <v>-477900000</v>
+        <v>-1076800000</v>
       </c>
       <c r="O2" t="n">
-        <v>249600000</v>
+        <v>459500000</v>
       </c>
       <c r="P2" t="n">
-        <v>59900000</v>
+        <v>290600000</v>
       </c>
       <c r="Q2" t="n">
-        <v>188300000</v>
+        <v>338000000</v>
       </c>
       <c r="R2" t="n">
-        <v>4900000</v>
+        <v>5200000</v>
       </c>
       <c r="S2" t="n">
-        <v>31000000</v>
+        <v>57700000</v>
       </c>
       <c r="T2" t="n">
-        <v>-200000</v>
+        <v>10600000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>11600000</v>
       </c>
       <c r="V2" t="n">
-        <v>-200000</v>
+        <v>-1000000</v>
       </c>
       <c r="W2" t="n">
-        <v>2800000</v>
+        <v>-22700000</v>
       </c>
       <c r="X2" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-29700000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>400000</v>
-      </c>
+        <v>-2000000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-800000</v>
+        <v>-2000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-166500000</v>
+        <v>-96200000</v>
       </c>
       <c r="AD2" t="n">
-        <v>45000000</v>
+        <v>66500000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-211500000</v>
+        <v>-162700000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-47500000</v>
+        <v>405700000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-172100000</v>
+        <v>-36800000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-185000000</v>
+        <v>-210500000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-233600000</v>
+        <v>-542200000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-400000</v>
+        <v>-32200000</v>
       </c>
       <c r="AK2" t="n">
-        <v>232200000</v>
+        <v>610900000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-350300000</v>
+        <v>-495600000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-115100000</v>
+        <v>-625300000</v>
       </c>
       <c r="AN2" t="n">
-        <v>181700000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-23800000</v>
-      </c>
+        <v>233800000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>390200000</v>
+        <v>406700000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>390200000</v>
+        <v>406700000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1100000</v>
+        <v>-1300000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2100000</v>
+        <v>-120800000</v>
       </c>
       <c r="AT2" t="n">
-        <v>19900000</v>
+        <v>6600000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-12600000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>32900000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-11000000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>49300000</v>
+        <v>883700000</v>
       </c>
     </row>
     <row r="3">
@@ -2689,147 +2689,147 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>241000000</v>
+        <v>-259800000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1076800000</v>
+        <v>-477900000</v>
       </c>
       <c r="D4" t="n">
-        <v>459500000</v>
+        <v>249600000</v>
       </c>
       <c r="E4" t="n">
-        <v>-164700000</v>
+        <v>-212300000</v>
       </c>
       <c r="F4" t="n">
-        <v>782300000</v>
+        <v>366500000</v>
       </c>
       <c r="G4" t="n">
-        <v>913800000</v>
+        <v>713700000</v>
       </c>
       <c r="H4" t="n">
-        <v>-22400000</v>
+        <v>-29500000</v>
       </c>
       <c r="I4" t="n">
-        <v>-109100000</v>
+        <v>-317700000</v>
       </c>
       <c r="J4" t="n">
-        <v>-805400000</v>
+        <v>-330100000</v>
       </c>
       <c r="K4" t="n">
-        <v>10600000</v>
+        <v>31400000</v>
       </c>
       <c r="L4" t="n">
-        <v>-617300000</v>
+        <v>-228300000</v>
       </c>
       <c r="M4" t="n">
-        <v>-617300000</v>
+        <v>-228300000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1076800000</v>
+        <v>-477900000</v>
       </c>
       <c r="O4" t="n">
-        <v>459500000</v>
+        <v>249600000</v>
       </c>
       <c r="P4" t="n">
-        <v>290600000</v>
+        <v>59900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>338000000</v>
+        <v>188300000</v>
       </c>
       <c r="R4" t="n">
-        <v>5200000</v>
+        <v>4900000</v>
       </c>
       <c r="S4" t="n">
-        <v>57700000</v>
+        <v>31000000</v>
       </c>
       <c r="T4" t="n">
-        <v>10600000</v>
+        <v>-200000</v>
       </c>
       <c r="U4" t="n">
-        <v>11600000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1000000</v>
+        <v>-200000</v>
       </c>
       <c r="W4" t="n">
-        <v>-22700000</v>
+        <v>2800000</v>
       </c>
       <c r="X4" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-29700000</v>
-      </c>
+        <v>2800000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-2000000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>-400000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>400000</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-2000000</v>
+        <v>-800000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-96200000</v>
+        <v>-166500000</v>
       </c>
       <c r="AD4" t="n">
-        <v>66500000</v>
+        <v>45000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-162700000</v>
+        <v>-211500000</v>
       </c>
       <c r="AF4" t="n">
-        <v>405700000</v>
+        <v>-47500000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-36800000</v>
+        <v>-172100000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-210500000</v>
+        <v>-185000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-542200000</v>
+        <v>-233600000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-32200000</v>
+        <v>-400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>610900000</v>
+        <v>232200000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-495600000</v>
+        <v>-350300000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-625300000</v>
+        <v>-115100000</v>
       </c>
       <c r="AN4" t="n">
-        <v>233800000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>181700000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-23800000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>406700000</v>
+        <v>390200000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>406700000</v>
+        <v>390200000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1300000</v>
+        <v>-1100000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-120800000</v>
+        <v>-2100000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6600000</v>
+        <v>19900000</v>
       </c>
       <c r="AU4" t="n">
-        <v>32900000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-11000000</v>
-      </c>
+        <v>-12600000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>883700000</v>
+        <v>49300000</v>
       </c>
     </row>
   </sheetData>
@@ -3369,187 +3369,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yongming  Qin', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2023, 'totalPay': 7300000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Udo  Langhans', 'title': 'Head of Commodity Risk Management', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chu  Yuejiang', 'age': 51, 'title': 'Executive Director', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yao  Xiang', 'age': 37, 'title': 'Executive Director', 'yearBorn': 1988, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Chong', 'title': 'IR Director', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yongming  Qin', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2023, 'totalPay': 7300000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Udo  Langhans', 'title': 'Head of Commodity Risk Management', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chu  Yuejiang', 'age': 51, 'title': 'Executive Director', 'yearBorn': 1974, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yao  Xiang', 'age': 37, 'title': 'Executive Director', 'yearBorn': 1988, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chun Yip Wun HKICPA', 'age': 50, 'title': 'Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Chong', 'title': 'IR Director', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.219</v>
+        <v>0.176</v>
       </c>
       <c r="AF2" t="n">
         <v>678000</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.0212</v>
@@ -3923,16 +3923,18 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>-1.1494242</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>CHIHO ENV</t>
-        </is>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>1743408508</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
@@ -3965,39 +3967,33 @@
       <c r="DJ2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DK2" t="n">
+        <v>-1.1494242</v>
       </c>
       <c r="DL2" t="n">
-        <v>1743408508</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Chiho Environmental Group Limited</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
+        <v>0.43</v>
+      </c>
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DN2" t="n">
+        <v>1278898200000</v>
+      </c>
+      <c r="DO2" t="n">
         <v>-0.004999995</v>
       </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.43 - 0.455</t>
+        </is>
+      </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>0.43 - 0.455</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
           <t>HKSE</t>
         </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -4005,37 +4001,41 @@
       <c r="DT2" t="n">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>0.43 - 0.455</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.025000006</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.054945067</v>
+      </c>
+      <c r="DX2" t="n">
         <v>0</v>
       </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.43 - 0.455</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.025000006</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.054945067</v>
-      </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>1724842822</v>
       </c>
       <c r="DZ2" t="n">
         <v>1724842822</v>
       </c>
-      <c r="EA2" t="n">
-        <v>1724842822</v>
-      </c>
-      <c r="EB2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EB2" t="n">
         <v>-0.01</v>
       </c>
-      <c r="ED2" t="n">
-        <v>0</v>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>CHIHO ENV</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Chiho Environmental Group Limited</t>
+        </is>
       </c>
       <c r="EE2" t="n">
         <v>0</v>
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="EH2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EJ2" t="b">
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="b">
         <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1278898200000</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
